--- a/23_Juli_Dataset_Gabungan_Performance_Emisi_PPO_v01.xlsx
+++ b/23_Juli_Dataset_Gabungan_Performance_Emisi_PPO_v01.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr dateCompatibility="0"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BRIN\RISET\2026\OREM\Paper\Dataset\23 Juli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57E3CEE4-FD49-4076-AAC5-7705836D0A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5EAA9203-D2CB-4932-BC83-32FBD0CB18DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,9 +18,6 @@
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
-      <x14:workbookPr/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -37,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="1200" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="90">
   <si>
     <t>PPO (%)</t>
   </si>
@@ -312,7 +309,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -346,15 +343,15 @@
   </fills>
   <borders count="2">
     <border>
-      <start/>
-      <end/>
+      <left/>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <start/>
-      <end/>
+      <left/>
+      <right/>
       <top style="medium">
         <color rgb="FF7F8C8D"/>
       </top>
@@ -500,7 +497,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelGabunganWPOBaru" displayName="TabelGabunganWPOBaru" ref="A1:AA210" headerRowDxfId="29" dataDxfId="28" totalsRowDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelGabunganWPOBaru" displayName="TabelGabunganWPOBaru" ref="A1:AA210" headerRowDxfId="29" dataDxfId="28" totalsRowDxfId="27">
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="PPO (%)" dataDxfId="26"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Load (%)" dataDxfId="25"/>
@@ -535,7 +532,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" name="ChatGPT">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
   <a:themeElements>
     <a:clrScheme name="ChatGPT">
       <a:dk1>
@@ -630,7 +627,7 @@
           <a:effectLst>
             <a:outerShdw blurRad="57150" dist="19050" dir="5400000">
               <a:srgbClr val="000000">
-                <a:alpha val="63%"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -642,32 +639,32 @@
         </a:solidFill>
         <a:solidFill>
           <a:schemeClr val="phClr">
-            <a:tint val="95%"/>
-            <a:satMod val="170%"/>
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:gradFill>
           <a:gsLst>
-            <a:gs pos="0%">
+            <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93%"/>
-                <a:shade val="98%"/>
-                <a:lumMod val="102%"/>
-                <a:satMod val="150%"/>
+                <a:tint val="93000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50%">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="98%"/>
-                <a:shade val="90%"/>
-                <a:lumMod val="103%"/>
-                <a:satMod val="130%"/>
+                <a:tint val="98000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="100%">
+            <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63%"/>
-                <a:satMod val="120%"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -682,7 +679,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA210"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
